--- a/data/trans_orig/P6707-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6707-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2012</t>
+          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2012 (tasa de respuesta: 98,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>38204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63502</t>
+          <t>65189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35911</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>60041</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54435</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83942</t>
+          <t>86435</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64969</t>
+          <t>65589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84974</t>
+          <t>85348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>65216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107941</t>
+          <t>106981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144360</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139075</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190428</t>
+          <t>190216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90169</t>
+          <t>92101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128758</t>
+          <t>130224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241820</t>
+          <t>241422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>305014</t>
+          <t>302208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63389</t>
+          <t>63442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97856</t>
+          <t>97522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50858</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81522</t>
+          <t>80771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120216</t>
+          <t>123377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168591</t>
+          <t>168837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187316</t>
+          <t>188937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240902</t>
+          <t>239236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99892</t>
+          <t>99847</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>141366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>299697</t>
+          <t>301070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>363337</t>
+          <t>364671</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158623</t>
+          <t>158656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206337</t>
+          <t>206013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>94948</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>134452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266096</t>
+          <t>264576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>325791</t>
+          <t>326687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246565</t>
+          <t>243835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302432</t>
+          <t>301249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137043</t>
+          <t>136038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182757</t>
+          <t>179234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396091</t>
+          <t>397381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>468897</t>
+          <t>469570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>46382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>29882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55116</t>
+          <t>54620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58257</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93087</t>
+          <t>90486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>52648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42585</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71923</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44280</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72134</t>
+          <t>72864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>94634</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134440</t>
+          <t>132908</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>71547</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105390</t>
+          <t>103934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60619</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116321</t>
+          <t>116058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160369</t>
+          <t>158022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97184</t>
+          <t>97481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132090</t>
+          <t>134194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58524</t>
+          <t>58666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89020</t>
+          <t>88399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>167073</t>
+          <t>165271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214502</t>
+          <t>215246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186599</t>
+          <t>185338</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246808</t>
+          <t>241912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158951</t>
+          <t>156869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209279</t>
+          <t>207847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>359914</t>
+          <t>361109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>435670</t>
+          <t>434095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>98397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145445</t>
+          <t>142433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70327</t>
+          <t>71925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106791</t>
+          <t>107373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>177472</t>
+          <t>179530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>236663</t>
+          <t>237383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>285676</t>
+          <t>285092</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>348203</t>
+          <t>349124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174273</t>
+          <t>173641</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>225402</t>
+          <t>226559</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>475907</t>
+          <t>472371</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>556979</t>
+          <t>556243</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266028</t>
+          <t>267402</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>330745</t>
+          <t>333139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>161267</t>
+          <t>156871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212049</t>
+          <t>207954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>441430</t>
+          <t>446187</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>527613</t>
+          <t>524914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>426143</t>
+          <t>423101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>497980</t>
+          <t>498657</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>257556</t>
+          <t>255575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>317395</t>
+          <t>314666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>698064</t>
+          <t>694660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>792876</t>
+          <t>792727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2016</t>
+          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60317</t>
+          <t>60700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>41027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30417</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55804</t>
+          <t>55661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>22474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>41998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>28931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65687</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32869</t>
+          <t>32199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44290</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>40177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>53871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158750</t>
+          <t>161279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211670</t>
+          <t>209124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,49 +4388,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>128196</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>110060</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149323</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>22,88%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128196</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>109271</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>150089</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>292</t>
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275890</t>
+          <t>280104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343622</t>
+          <t>344574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118012</t>
+          <t>117746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160369</t>
+          <t>159161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73817</t>
+          <t>73280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109655</t>
+          <t>110571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202496</t>
+          <t>202421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257068</t>
+          <t>257074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218726</t>
+          <t>219418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274284</t>
+          <t>276626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163424</t>
+          <t>161820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209325</t>
+          <t>204801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>399621</t>
+          <t>393619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>465848</t>
+          <t>465245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162456</t>
+          <t>164854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212759</t>
+          <t>213056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>124160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167612</t>
+          <t>164417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>300976</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>365778</t>
+          <t>363640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141651</t>
+          <t>145260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193420</t>
+          <t>192469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89574</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127185</t>
+          <t>128230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246515</t>
+          <t>245150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>304718</t>
+          <t>306595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>35460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>62188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53984</t>
+          <t>54806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82918</t>
+          <t>84876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,47 +5105,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>17,77%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>27,52%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>115329</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>97423</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>136559</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>17,5%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>26,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>115329</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>96815</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>138094</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38566</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67022</t>
+          <t>67148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55643</t>
+          <t>54177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>76004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110733</t>
+          <t>112729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86014</t>
+          <t>86013</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123257</t>
+          <t>121993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>54436</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82434</t>
+          <t>83289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>150745</t>
+          <t>148943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195670</t>
+          <t>192984</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59151</t>
+          <t>59947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>91037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50498</t>
+          <t>50948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78720</t>
+          <t>79578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117721</t>
+          <t>117733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160347</t>
+          <t>159333</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61345</t>
+          <t>58833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91962</t>
+          <t>91351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53977</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>83329</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121569</t>
+          <t>123281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165418</t>
+          <t>167929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>233208</t>
+          <t>231483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>291832</t>
+          <t>293674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189172</t>
+          <t>186212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>240693</t>
+          <t>239928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>437091</t>
+          <t>440038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>513069</t>
+          <t>517511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194140</t>
+          <t>193716</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252860</t>
+          <t>248005</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124238</t>
+          <t>124069</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>167229</t>
+          <t>168324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>330518</t>
+          <t>329554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>406543</t>
+          <t>396522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>347267</t>
+          <t>348404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>415674</t>
+          <t>417839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>242758</t>
+          <t>243599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>299354</t>
+          <t>302826</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>607707</t>
+          <t>607805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>696606</t>
+          <t>699496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255201</t>
+          <t>253031</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315617</t>
+          <t>315176</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>193743</t>
+          <t>192202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>246194</t>
+          <t>246340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>463394</t>
+          <t>461049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>544525</t>
+          <t>543301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>241457</t>
+          <t>244044</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>301662</t>
+          <t>305240</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160024</t>
+          <t>160443</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>210768</t>
+          <t>210517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>418641</t>
+          <t>421930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>497419</t>
+          <t>498171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2023</t>
+          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15044</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121265</t>
+          <t>121319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>445500</t>
+          <t>456527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71090</t>
+          <t>70126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96934</t>
+          <t>97784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213075</t>
+          <t>219414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>593421</t>
+          <t>605197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63862</t>
+          <t>62939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46190</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104572</t>
+          <t>101157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161259</t>
+          <t>158630</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39708</t>
+          <t>38853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61574</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54601</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203068</t>
+          <t>197195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96362</t>
+          <t>96109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>27203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121590</t>
+          <t>121667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>94533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>41888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123963</t>
+          <t>121391</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>38713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40409</t>
+          <t>40820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65786</t>
+          <t>66647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>28385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32444</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67862</t>
+          <t>68693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57006</t>
+          <t>58253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>48655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>34524</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76769</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152413</t>
+          <t>155584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>544014</t>
+          <t>542617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98463</t>
+          <t>98333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>130012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>275519</t>
+          <t>276408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>738340</t>
+          <t>743360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74660</t>
+          <t>75992</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37417</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60086</t>
+          <t>60976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127444</t>
+          <t>128120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>46582</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192430</t>
+          <t>194269</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67215</t>
+          <t>67296</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93927</t>
+          <t>93899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>100092</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>266154</t>
+          <t>265251</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26578</t>
+          <t>28719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126781</t>
+          <t>123577</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>43892</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67608</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61778</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179534</t>
+          <t>177078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32290</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147025</t>
+          <t>143551</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,17 +9213,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>145109</t>
+          <t>145110</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64259</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>197638</t>
+          <t>199713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6707-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6707-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29157</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21079</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42621</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>64098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35140</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60041</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55111</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>85919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>39058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31794</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65589</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58047</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>83987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42320</t>
+          <t>41714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65216</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106981</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142284</t>
+          <t>143155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142284</t>
+          <t>141624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190216</t>
+          <t>191710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92101</t>
+          <t>91752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130224</t>
+          <t>128958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241422</t>
+          <t>236950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302208</t>
+          <t>301997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63442</t>
+          <t>63979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97522</t>
+          <t>99984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50209</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80771</t>
+          <t>82354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123377</t>
+          <t>123544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168837</t>
+          <t>170147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188937</t>
+          <t>187636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239236</t>
+          <t>237206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99847</t>
+          <t>98721</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141366</t>
+          <t>139476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>301070</t>
+          <t>299126</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364671</t>
+          <t>366901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158656</t>
+          <t>159082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206013</t>
+          <t>207532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94948</t>
+          <t>96111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134452</t>
+          <t>136241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264576</t>
+          <t>265527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326687</t>
+          <t>331447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243835</t>
+          <t>245186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301249</t>
+          <t>303133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136038</t>
+          <t>137622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179234</t>
+          <t>180836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397381</t>
+          <t>395449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>469570</t>
+          <t>465447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>46125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29882</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>57773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90486</t>
+          <t>93450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27094</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71238</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45477</t>
+          <t>44193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72864</t>
+          <t>72168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94634</t>
+          <t>95565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132908</t>
+          <t>133419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71547</t>
+          <t>70740</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>104749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>62608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116058</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158022</t>
+          <t>157554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97481</t>
+          <t>97915</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134194</t>
+          <t>133988</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58666</t>
+          <t>57292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88399</t>
+          <t>88955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>165271</t>
+          <t>165939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215246</t>
+          <t>212654</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185338</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241912</t>
+          <t>246994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156869</t>
+          <t>156560</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207847</t>
+          <t>206788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>361109</t>
+          <t>358545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434095</t>
+          <t>432404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98397</t>
+          <t>99802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142433</t>
+          <t>142718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>69934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107373</t>
+          <t>106299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>179094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237383</t>
+          <t>235389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>285092</t>
+          <t>284768</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>349124</t>
+          <t>350651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>173641</t>
+          <t>175114</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>226559</t>
+          <t>228201</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>472371</t>
+          <t>472135</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>556243</t>
+          <t>555142</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>267402</t>
+          <t>267633</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>333139</t>
+          <t>329746</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156871</t>
+          <t>158666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207954</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>446187</t>
+          <t>443227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>524914</t>
+          <t>522750</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>423101</t>
+          <t>424969</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>498657</t>
+          <t>499198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>255575</t>
+          <t>253507</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>314666</t>
+          <t>312316</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>694660</t>
+          <t>696781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>792727</t>
+          <t>790748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35786</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60700</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41027</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55661</t>
+          <t>55085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>41115</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>65105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43930</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40177</t>
+          <t>41682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53871</t>
+          <t>53280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161279</t>
+          <t>161006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209124</t>
+          <t>211282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110060</t>
+          <t>108795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149323</t>
+          <t>149893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280104</t>
+          <t>278881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344574</t>
+          <t>344951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117746</t>
+          <t>121226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159161</t>
+          <t>162653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73280</t>
+          <t>73916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110571</t>
+          <t>110861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202421</t>
+          <t>203654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257074</t>
+          <t>260004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219418</t>
+          <t>218306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>276626</t>
+          <t>275264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>159505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>204801</t>
+          <t>205480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>393619</t>
+          <t>393827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>465245</t>
+          <t>463578</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164854</t>
+          <t>164362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213056</t>
+          <t>214267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124160</t>
+          <t>122496</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164417</t>
+          <t>165724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>300716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363640</t>
+          <t>366740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145260</t>
+          <t>146134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192469</t>
+          <t>192613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89521</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128230</t>
+          <t>126377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>245150</t>
+          <t>246563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306595</t>
+          <t>308027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35460</t>
+          <t>34121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62188</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54806</t>
+          <t>54956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84876</t>
+          <t>84495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97423</t>
+          <t>97083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136559</t>
+          <t>139737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>37899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67148</t>
+          <t>65049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54177</t>
+          <t>53131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76004</t>
+          <t>75901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112729</t>
+          <t>112479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86013</t>
+          <t>86432</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121993</t>
+          <t>121290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83289</t>
+          <t>82998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148943</t>
+          <t>149692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192984</t>
+          <t>196229</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59947</t>
+          <t>58297</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91037</t>
+          <t>91348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>50705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79578</t>
+          <t>79952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117733</t>
+          <t>116242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>159333</t>
+          <t>159111</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58833</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91351</t>
+          <t>91942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>81890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123281</t>
+          <t>121115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167929</t>
+          <t>164412</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>231483</t>
+          <t>230112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>293674</t>
+          <t>292936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186212</t>
+          <t>187685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239928</t>
+          <t>240747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440038</t>
+          <t>434993</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>517511</t>
+          <t>515941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193716</t>
+          <t>192950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248005</t>
+          <t>249847</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124069</t>
+          <t>123146</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>168324</t>
+          <t>168161</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>329554</t>
+          <t>330849</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>396522</t>
+          <t>402418</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>348404</t>
+          <t>349576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>417839</t>
+          <t>418776</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>243599</t>
+          <t>245137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>302826</t>
+          <t>300722</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>607805</t>
+          <t>610165</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>699496</t>
+          <t>699006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>253031</t>
+          <t>254030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315176</t>
+          <t>314675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>192202</t>
+          <t>193051</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>246340</t>
+          <t>247005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>461049</t>
+          <t>462146</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>543301</t>
+          <t>540165</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244044</t>
+          <t>243053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>305240</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160443</t>
+          <t>160399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>210517</t>
+          <t>209770</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>421930</t>
+          <t>415723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>498171</t>
+          <t>498451</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>313310</t>
+          <t>77632</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121319</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>456527</t>
+          <t>96870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84122</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70126</t>
+          <t>83884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97784</t>
+          <t>112863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>397432</t>
+          <t>175391</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219414</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>605197</t>
+          <t>198281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62939</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34839</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46196</t>
+          <t>48669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>63816</t>
+          <t>72391</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>56535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>89941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78517</t>
+          <t>84450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>68061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158630</t>
+          <t>102309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49181</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>41044</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59975</t>
+          <t>63493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>127698</t>
+          <t>136369</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>119539</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197195</t>
+          <t>161902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>49482</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96109</t>
+          <t>64558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>24233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39199</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>81925</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27203</t>
+          <t>64937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121667</t>
+          <t>98621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44561</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94533</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>86205</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>69036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121391</t>
+          <t>107637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>229450</t>
+          <t>254877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>229450</t>
+          <t>254877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229450</t>
+          <t>254877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>741254</t>
+          <t>552281</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>741254</t>
+          <t>552281</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>741254</t>
+          <t>552281</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38713</t>
+          <t>42298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>56177</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40820</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66647</t>
+          <t>70496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>31507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41538</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>57487</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68693</t>
+          <t>72007</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32461</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>32944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>50326</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58253</t>
+          <t>62674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>35652</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48655</t>
+          <t>55588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25066</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34524</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>60717</t>
+          <t>68349</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76351</t>
+          <t>86506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>347828</t>
+          <t>120472</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155584</t>
+          <t>98252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>542617</t>
+          <t>143184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>131737</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98333</t>
+          <t>113414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130012</t>
+          <t>148807</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>461399</t>
+          <t>252208</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276408</t>
+          <t>223395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>743360</t>
+          <t>280307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75992</t>
+          <t>70780</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>47548</t>
+          <t>54124</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>67306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>106548</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44836</t>
+          <t>88159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128120</t>
+          <t>128234</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116724</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46582</t>
+          <t>103883</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>194269</t>
+          <t>146368</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79738</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67296</t>
+          <t>70551</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93899</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>196462</t>
+          <t>209729</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>96131</t>
+          <t>185002</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>265251</t>
+          <t>236845</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>74054</t>
+          <t>80982</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>65448</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123577</t>
+          <t>100786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>128578</t>
+          <t>139613</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>117788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177078</t>
+          <t>163564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>87135</t>
+          <t>100583</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32565</t>
+          <t>79348</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143551</t>
+          <t>122079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>78488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>145110</t>
+          <t>164376</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>138263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199713</t>
+          <t>192841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>353354</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>353354</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>353354</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1023315</t>
+          <t>872475</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1023315</t>
+          <t>872475</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1023315</t>
+          <t>872475</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
